--- a/WEDDING_GUEST_LIST.xlsx
+++ b/WEDDING_GUEST_LIST.xlsx
@@ -631,10 +631,10 @@
     <t xml:space="preserve">Charnae</t>
   </si>
   <si>
-    <t xml:space="preserve">Olivia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yamilette</t>
+    <t xml:space="preserve">Olivia Leon Vitervo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yamilet Macias</t>
   </si>
   <si>
     <t xml:space="preserve">Kulsoom</t>

--- a/WEDDING_GUEST_LIST.xlsx
+++ b/WEDDING_GUEST_LIST.xlsx
@@ -439,7 +439,7 @@
     <t xml:space="preserve">Linda</t>
   </si>
   <si>
-    <t xml:space="preserve">Shawn</t>
+    <t xml:space="preserve">Shaun</t>
   </si>
   <si>
     <t xml:space="preserve">Mia</t>

--- a/WEDDING_GUEST_LIST.xlsx
+++ b/WEDDING_GUEST_LIST.xlsx
@@ -439,7 +439,7 @@
     <t xml:space="preserve">Linda</t>
   </si>
   <si>
-    <t xml:space="preserve">Shaun</t>
+    <t xml:space="preserve">Linda's Husband – Shaun</t>
   </si>
   <si>
     <t xml:space="preserve">Mia</t>
